--- a/tame_output/ON/bt/strategyON_20240222.xlsx
+++ b/tame_output/ON/bt/strategyON_20240222.xlsx
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>1.516669646030502</v>
+        <v>1.516891274803419</v>
       </c>
       <c r="E1881" t="n">
-        <v>3.778147446757502</v>
+        <v>3.778236098266669</v>
       </c>
       <c r="F1881" t="n">
-        <v>2.438899261275111</v>
+        <v>2.439120890048028</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.635175569424115</v>
+        <v>4.635308546687866</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240222.xlsx
+++ b/tame_output/ON/bt/strategyON_20240222.xlsx
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.7%</t>
+          <t>447.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>1.516891274803419</v>
+        <v>1.51710621060134</v>
       </c>
       <c r="E1881" t="n">
-        <v>3.778236098266669</v>
+        <v>3.778322072585838</v>
       </c>
       <c r="F1881" t="n">
-        <v>2.439120890048028</v>
+        <v>2.439335825845949</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.635308546687866</v>
+        <v>4.635437508166619</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240222.xlsx
+++ b/tame_output/ON/bt/strategyON_20240222.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.6%</t>
+          <t>448.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.6%</t>
+          <t>131.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>1.51710621060134</v>
+        <v>1.450559386406132</v>
       </c>
       <c r="E1881" t="n">
-        <v>3.778322072585838</v>
+        <v>3.751703342907755</v>
       </c>
       <c r="F1881" t="n">
-        <v>2.439335825845949</v>
+        <v>2.372789001650741</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.635437508166619</v>
+        <v>4.595509413649494</v>
       </c>
     </row>
   </sheetData>
